--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.61765939331622</v>
+        <v>5.625369651413886</v>
       </c>
       <c r="D2" t="n">
-        <v>69.81277138343626</v>
+        <v>11.34457534980839</v>
       </c>
       <c r="E2" t="n">
-        <v>10.50292668681682</v>
+        <v>1.706725586607734</v>
       </c>
       <c r="F2" t="n">
-        <v>6.262483893457175</v>
+        <v>1.017653632686792</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.20585553136895</v>
+        <v>9.620951523847454</v>
       </c>
       <c r="D3" t="n">
-        <v>53.4881653948412</v>
+        <v>8.691826876661695</v>
       </c>
       <c r="E3" t="n">
-        <v>10.50292668681682</v>
+        <v>1.706725586607734</v>
       </c>
       <c r="F3" t="n">
-        <v>6.262483893457175</v>
+        <v>1.017653632686792</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.99455661216921</v>
+        <v>5.361615449477496</v>
       </c>
       <c r="D4" t="n">
-        <v>55.71024773230506</v>
+        <v>9.052915256499572</v>
       </c>
       <c r="E4" t="n">
-        <v>10.50292668681682</v>
+        <v>1.706725586607734</v>
       </c>
       <c r="F4" t="n">
-        <v>6.262483893457175</v>
+        <v>1.017653632686792</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.89310085554872</v>
+        <v>7.457628889026668</v>
       </c>
       <c r="D5" t="n">
-        <v>59.29749612456631</v>
+        <v>9.635843120242026</v>
       </c>
       <c r="E5" t="n">
-        <v>10.50292668681682</v>
+        <v>1.706725586607734</v>
       </c>
       <c r="F5" t="n">
-        <v>6.262483893457175</v>
+        <v>1.017653632686792</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
